--- a/dentist_forms/013_dentist_job_application_form--dentist_forms.xlsx
+++ b/dentist_forms/013_dentist_job_application_form--dentist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit Button</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submit Error</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submit Cancel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submit Cancel Message</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submit Success Message</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Submit Success Message Default</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Form Submit Error</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Form Submit Success</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'partially'}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Partially'}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'partially'}</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Partially'}</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
